--- a/output/261001-전남대-손현철/261001-세트2-비교견적서2.xlsx
+++ b/output/261001-전남대-손현철/261001-세트2-비교견적서2.xlsx
@@ -367,175 +367,175 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -562,9 +562,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>140400</xdr:colOff>
+      <xdr:colOff>140040</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>209520</xdr:rowOff>
+      <xdr:rowOff>209160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -578,7 +578,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5720040" y="476640"/>
-          <a:ext cx="960120" cy="1104480"/>
+          <a:ext cx="959760" cy="1104120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -865,7 +865,7 @@
       </c>
       <c r="E10" s="16" t="n">
         <f aca="false">N26</f>
-        <v>2287120</v>
+        <v>2540120</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
@@ -877,7 +877,7 @@
       </c>
       <c r="L10" s="17" t="n">
         <f aca="false">N26</f>
-        <v>2287120</v>
+        <v>2540120</v>
       </c>
       <c r="M10" s="17"/>
       <c r="N10" s="17"/>
@@ -938,12 +938,12 @@
         <v>20</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>95900</v>
+        <v>105900</v>
       </c>
       <c r="N13" s="27"/>
       <c r="O13" s="28" t="n">
         <f aca="false">M13*L13</f>
-        <v>1918000</v>
+        <v>2118000</v>
       </c>
       <c r="P13" s="28"/>
     </row>
@@ -969,12 +969,12 @@
         <v>1</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>67300</v>
+        <v>77300</v>
       </c>
       <c r="N14" s="27"/>
       <c r="O14" s="28" t="n">
         <f aca="false">M14*L14</f>
-        <v>67300</v>
+        <v>77300</v>
       </c>
       <c r="P14" s="28"/>
       <c r="R14" s="2"/>
@@ -1006,12 +1006,12 @@
         <v>1</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>59600</v>
+        <v>69600</v>
       </c>
       <c r="N15" s="27"/>
       <c r="O15" s="28" t="n">
         <f aca="false">M15*L15</f>
-        <v>59600</v>
+        <v>69600</v>
       </c>
       <c r="P15" s="28"/>
     </row>
@@ -1037,12 +1037,12 @@
         <v>1</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>34300</v>
+        <v>44300</v>
       </c>
       <c r="N16" s="27"/>
       <c r="O16" s="28" t="n">
         <f aca="false">M16*L16</f>
-        <v>34300</v>
+        <v>44300</v>
       </c>
       <c r="P16" s="28"/>
     </row>
@@ -1194,7 +1194,7 @@
       <c r="M24" s="21"/>
       <c r="N24" s="39" t="n">
         <f aca="false">SUM(O13:P23)</f>
-        <v>2079200</v>
+        <v>2309200</v>
       </c>
       <c r="O24" s="39"/>
       <c r="P24" s="39"/>
@@ -1219,7 +1219,7 @@
       <c r="M25" s="21"/>
       <c r="N25" s="39" t="n">
         <f aca="false">N24*0.1</f>
-        <v>207920</v>
+        <v>230920</v>
       </c>
       <c r="O25" s="39"/>
       <c r="P25" s="39"/>
@@ -1246,7 +1246,7 @@
       <c r="M26" s="21"/>
       <c r="N26" s="39" t="n">
         <f aca="false">SUM(N24:N25)</f>
-        <v>2287120</v>
+        <v>2540120</v>
       </c>
       <c r="O26" s="39"/>
       <c r="P26" s="39"/>
